--- a/MALUNA_rituals.xlsx
+++ b/MALUNA_rituals.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -487,15 +487,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>устала</t>
+          <t>устала, тревожно</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -505,19 +505,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>свечи MALUNA, ванна, увлажняющий крем MALUNA</t>
+          <t>чай</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Вечер для восстановления</t>
+          <t>Пауза с чаем</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Зажги свечу MALUNA и приглуши свет. Наполни ванну тёплой водой и полежи в ней 15–20 минут, отпуская напряжение из тела.
-После — нанеси увлажняющий крем MALUNA лёгкими движениями снизу вверх, будто заботясь о себе заново.
-Останься в тишине ещё немного, слушая, как горит свеча.</t>
+          <t>Завари чашку тёплого чая и на пять минут отложи телефон. Сядь удобно, обхвати чашку ладонями, почувствуй тепло. Сделай три медленных вдоха и выдоха, наблюдая за паром. Этого времени достаточно, чтобы тело и мысли немного замедлились.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -532,15 +530,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>вечер, день</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>тревожно, устала</t>
+          <t>устала</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -550,19 +548,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>свечи MALUNA, чай</t>
+          <t>душ, гидрофильное масло MALUNA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Пять минут тишины</t>
+          <t>Тёплый ритуал расслабления</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Завари чай и зажги свечу MALUNA.
-Поставь телефон экраном вниз и просто смотри на пламя, пока чай остывает. Ничего не решай, никуда не спеши.
-Пять минут — это уже пауза 🕯</t>
+          <t>Включи тёплую воду. Перед душем очисти лицо гидрофильным маслом MALUNA — мягкими круговыми движениями, не торопясь. Встань под душ на 10–15 минут, позволяя воде снять напряжение дня. Заверши тишиной: не включай телефон сразу.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -577,37 +573,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>утро</t>
+          <t>вечер</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>устала, любое</t>
+          <t>устала</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>взбодриться</t>
+          <t>отдохнуть</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>кофе, душ</t>
+          <t>свечи MALUNA, ванна, увлажняющий крем MALUNA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Быстрый старт</t>
+          <t>Вечер для восстановления</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Включи прохладную воду в конце душа — на десять секунд, не дольше. Тело проснётся само.
-Свари кофе и выпей его стоя у окна, не отвлекаясь на ленту.
-Утро уже началось ✨</t>
+          <t>Зажги свечу MALUNA и приглуши свет. Наполни ванну тёплой водой и полежи в ней 15–20 минут, отпуская напряжение из тела. После — нанеси увлажняющий крем MALUNA лёгкими движениями снизу вверх, будто заботясь о себе заново. Останься в тишине ещё немного, слушая, как горит свеча.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -622,37 +616,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>утро, день</t>
+          <t>любое</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>хочется вдохновения, радостно</t>
+          <t>тревожно</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>взбодриться</t>
+          <t>отдохнуть</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>кофе, свечи MALUNA, душ</t>
+          <t>чай</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Разгон дня</t>
+          <t>Дыхание и тепло</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Прими душ и, пока волосы сохнут, зажги свечу MALUNA — пусть в комнате появится запах и свет.
-Свари кофе. Возьми лист бумаги и запиши три вещи, которые хочешь успеть сегодня. Только три, не больше.
-Теперь у дня есть форма 🕯</t>
+          <t>Возьми кружку чая и сядь у окна. Дыши по схеме: вдох на 4 счёта, задержка на 4, выдох на 6. Повтори 5 раз, ощущая, как с каждым выдохом тело чуть тяжелеет и успокаивается. Простой способ вернуть себе почву под ногами.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -667,37 +659,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>устала, любое</t>
+          <t>устала, хочется вдохновения</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>позаботиться о коже</t>
+          <t>взбодриться</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>гидрофильное масло MALUNA, очищающий гель MALUNA, увлажняющий крем MALUNA</t>
+          <t>кофе</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Вечернее очищение</t>
+          <t>Быстрый заряд</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Нанеси гидрофильное масло MALUNA на сухую кожу и помассируй лицо круговыми движениями минуту — не торопись, это самая приятная часть.
-Смой тёплой водой и пройдись очищающим гелем MALUNA.
-Промокни лицо полотенцем и нанеси увлажняющий крем MALUNA, пока кожа ещё влажная — так он работает лучше.</t>
+          <t>Свари кофе и выпей его осознанно, не отвлекаясь на телефон. Пока пьёшь, сделай несколько потягиваний рук вверх и наклонов в стороны. Открой окно на минуту, впусти свежий воздух. Этого хватит, чтобы почувствовать себя включённой в день.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -712,37 +702,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>утро, день</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>устала</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>позаботиться о коже</t>
+          <t>взбодриться</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>увлажняющий крем MALUNA</t>
+          <t>душ, очищающий гель MALUNA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Минута для кожи</t>
+          <t>Контрастная бодрость</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Согрей немного увлажняющего крема MALUNA между ладонями.
-Нанеси на лицо и шею мягкими движениями снизу вверх, задержись на секунду у висков.
-Вдохни глубоко. Всё, забота случилась 💜</t>
+          <t>Прими душ, в конце на 10–15 секунд включи прохладную воду — это мягко взбодрит тело. Умойся очищающим гелем MALUNA, уделяя внимание массажным движениям. Заверши стаканом воды. Тело и разум проснутся вместе.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -757,7 +745,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>вечер</t>
+          <t>утро</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -765,29 +753,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>хочется вдохновения, радостно</t>
+          <t>хочется вдохновения</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>создать уют</t>
+          <t>взбодриться</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>свечи MALUNA, чай</t>
+          <t>душ, очищающий гель MALUNA, увлажняющий крем MALUNA, кофе</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Уютный вечер</t>
+          <t>Полное пробуждение</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Убери со стола всё лишнее — уют начинается с пустой поверхности.
-Зажги две свечи MALUNA и выключи верхний свет. Завари чай и достань то, что давно откладывала: книгу, пластинку, старый альбом с фотографиями.
-Проведи так полчаса, никуда не переключаясь. Дом ответит теплом ✨</t>
+          <t>Начни с душа, очистив кожу гелем MALUNA — дай себе время прочувствовать текстуру и аромат. После нанеси увлажняющий крем MALUNA, лёгким массажем стимулируя лицо. Завари кофе и выпей его, стоя у окна, наблюдая за городом. Составь короткий список из трёх вещей, которые хочется сделать сегодня.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -798,11 +784,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>день</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -810,29 +796,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>любое</t>
+          <t>хочется вдохновения</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>создать уют</t>
+          <t>взбодриться</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>свечи MALUNA, чай, кофе</t>
+          <t>чай</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Уют за пять минут</t>
+          <t>Глоток вдохновения</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Зажги свечу MALUNA и выключи верхний свет — комната сразу станет мягче.
-Налей себе чай или кофе и сядь там, где нравится больше всего.
-Пять минут ничего не делай. Дом это оценит 🕯</t>
+          <t>Завари чай нового вкуса, который давно хотела попробовать. Пока он заваривается, выйди на балкон или к окну и посмотри вдаль минуту. Возвращаясь, сделай первый глоток осознанно, отмечая вкус. Маленькая новизна освежает восприятие дня.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -843,44 +827,859 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>очищающий гель MALUNA</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Мини-уход</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Умойся очищающим гелем MALUNA, уделяя коже чуть больше внимания, чем обычно — мягкими круговыми движениями по 30 секунд. Ополосни лицо прохладной водой, чтобы взбодрить кожу. Промокни полотенцем, не растирая. Пять минут — а кожа уже благодарна.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>очищающий гель MALUNA, увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Двойной уход</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Очисти лицо гелем MALUNA, смывая макияж и усталость дня. Промокни кожу и нанеси увлажняющий крем MALUNA лёгкими похлопывающими движениями, давая ему впитаться. Уделяй особое внимание области вокруг глаз. Дай себе пару минут прежде чем вернуться к делам.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>гидрофильное масло MALUNA, очищающий гель MALUNA, увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ритуал двойного очищения</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Начни с гидрофильного масла MALUNA — им растворяются макияж и загрязнения даже там, где обычные средства не справляются. Смой тёплой водой, затем очисти кожу гелем MALUNA. Заверши нанесением увлажняющего крема MALUNA, массируя лицо снизу вверх 2–3 минуты. Такой ритуал — как визит к косметологу, только дома.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>день, вечер</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C13" t="n">
         <v>15</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>тревожно, устала</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>тревожно</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>гидрофильное масло MALUNA</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Забота как опора</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Нанеси гидрофильное масло MALUNA на сухую кожу и помассируй лицо круговыми движениями 2–3 минуты — это ощутимо расслабляет. Смой тёплой водой, наблюдая, как вместе с маслом смывается и напряжение. Медленный, тактильный ритуал помогает вернуться в тело, когда мысли тревожны.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>создать уют</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>свечи MALUNA, чай, кофе</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Дом, который обнимает</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Открой окно на пять минут — впусти свежий воздух, даже если на улице прохладно.
-Пока проветривается, поставь чайник. Закрой окно, зажги свечу MALUNA и налей себе чай или кофе.
-Сядь там, где тебе удобнее всего, и побудь немного 🕯</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>свечи MALUNA, чай</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Тёплый вечерний штрих</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Зажги свечу MALUNA и завари чай. Приглуши верхний свет — пусть комната освещается только пламенем и настольной лампой. Сядь на пару минут без телефона, просто наблюдая за огнём. Маленький ритуал, который превращает обычный вечер в момент для себя.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>15</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>радостно</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>создать уют</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>свечи MALUNA, кофе</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Уютный вечер с собой</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Зажги свечу MALUNA, включи любимую музыку или подкаст. Завари кофе или чай и устройся поудобнее — с пледом, книгой или просто с мыслями. Дай себе разрешение ничего не делать эти 15 минут, кроме как наслаждаться атмосферой.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>создать уют</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>свечи MALUNA, ванна, увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Домашний спа-вечер</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Зажги несколько свечей MALUNA по комнате и наполни ванну тёплой водой. Полежи в ней 15–20 минут, включив спокойную музыку. После — нанеси увлажняющий крем MALUNA, продлевая ощущение заботы о себе. Останься в этой атмосфере ещё немного, никуда не торопясь.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>день</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>радостно</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>создать уют</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>чай</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Маленькая радость</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Завари любимый чай и выбери самую красивую чашку, какая есть дома. Устройся у окна или в любимом кресле на пять минут. Позволь себе просто побыть в хорошем настроении, ничего не делая специально. Такие маленькие паузы делают день теплее.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>тревожно</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>создать уют</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>свечи MALUNA</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Тихая гавань</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Зажги свечу MALUNA и выключи яркий свет. Сядь рядом, ничего не делая — просто смотри на пламя 10–15 минут. Дыши медленно, отпуская мысли одну за другой. Огонь свечи — хороший якорь, когда внутри неспокойно.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>утро</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>хочется вдохновения</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>отдохнуть</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>чай</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Тихое утро</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Завари чай и выйди на пять минут туда, где тихо — на балкон, к окну, в кресло. Не бери телефон, просто наблюдай за тем, что вокруг: свет, звуки, запахи. Позволь мыслям течь свободно, без цели. Иногда вдохновение приходит именно в паузе.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>день</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>15</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>радостно</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>взбодриться</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>душ, очищающий гель MALUNA</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Свежий заряд радости</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Прими бодрящий душ, очистив кожу гелем MALUNA. Включи любимую музыку и позволь себе немного потанцевать, пока умываешься и одеваешься. Хорошее настроение — отличный повод добавить в рутину чуть больше удовольствия. Заверши стаканом воды или лёгким перекусом.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>15</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>устала</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>гидрофильное масло MALUNA, увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Восстановление к ночи</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Сними макияж и усталость дня гидрофильным маслом MALUNA, массируя лицо медленными движениями. Смой тёплой водой и нанеси увлажняющий крем MALUNA, уделяя внимание области вокруг глаз. Этот короткий ритуал помогает не только коже, но и настрою — как знак, что день завершён.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>устала, тревожно</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>отдохнуть</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>душ</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Тёплые струи</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Встань под тёплый душ и на пять минут ни о чём не думай — просто ощущай воду на коже. Наклони голову назад, дай воде стекать по плечам, снимая напряжение. Выключи воду медленно, не торопясь одеваться. Такая короткая пауза под водой работает как перезагрузка.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>устала</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>отдохнуть</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ванна</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Просто вода</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Наполни ванну тёплой водой и погрузись в неё на 15 минут, ничего не добавляя — только тепло и тишина. Закрой глаза, дай телу расслабиться слой за слоем: сначала плечи, потом шея, потом лицо. Выходя, не спеши включать яркий свет. Иногда самый честный отдых — это просто вода и тишина.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>утро</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>5</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>устала</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>взбодриться</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>душ</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Прохладный финал</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Прими обычный душ, а в конце на 15–20 секунд включи прохладную воду — на стопы, затем на плечи. Дыши глубже обычного в этот момент. Это резко и бережно включает тело в режим бодрствования. После — утренние дела пройдут легче.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>15</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>гидрофильное масло MALUNA</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Только масло</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Нанеси гидрофильное масло MALUNA на сухую кожу лица и помассируй 2–3 минуты круговыми движениями — от центра к вискам. Добавь немного воды и помассируй ещё раз, дав маслу превратиться в молочко. Смой тёплой водой полностью. Кожа станет мягкой без необходимости в других средствах.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Слой заботы</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Нанеси увлажняющий крем MALUNA на лицо и шею лёгкими похлопывающими движениями снизу вверх. Задержись на несколько секунд у скул и вокруг глаз, где кожа тоньше всего. Дай крему впитаться полностью, прежде чем прикасаться к лицу дальше. Простое действие, которое за минуту меняет ощущение кожи.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>вечер</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>30</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>создать уют</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ванна</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Долгое погружение</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Наполни ванну тёплой водой и позволь себе провести в ней 20–25 минут без телефона и часов. Включи тихую музыку, если хочется, или оставь только звук воды. Дай мыслям идти своим чередом, не удерживая ни одну из них. После — заверни себя в самое мягкое полотенце, какое есть.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>любое</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>тревожно</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>позаботиться о коже</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>увлажняющий крем MALUNA</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Опора в прикосновении</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Нанеси увлажняющий крем MALUNA на руки и лицо, сосредотачиваясь только на ощущениях от прикосновений. Считай про себя движения — это помогает переключить внимание с тревожных мыслей на тело. Заверши, слегка прижав ладони к щекам на несколько секунд. Иногда забота о коже — это ещё и забота о нервной системе.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>да</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>утро</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>хочется вдохновения</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>взбодриться</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>душ</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Душ с намерением</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Прими душ чуть дольше обычного, представляя, будто вода смывает не только усталость, но и вчерашние заботы. Проговори про себя одну вещь, которую хочешь сделать сегодня по-новому. Выйди из душа с ощущением чистого листа. Иногда для вдохновения достаточно немного ритуальности в обычных действиях.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>да</t>
         </is>
